--- a/Result/profitability/8048.xlsx
+++ b/Result/profitability/8048.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5475</v>
+        <v>0.6449999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>34.2325</v>
+        <v>34.58625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5812499999999999</v>
+        <v>0.60375</v>
       </c>
       <c r="N3" t="n">
-        <v>34.72625</v>
+        <v>34.615</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.55</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>34.93875</v>
+        <v>35.06874999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0.58</v>
+        <v>0.68875</v>
       </c>
       <c r="N5" t="n">
-        <v>35.84375</v>
+        <v>36.24375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0.60375</v>
+        <v>0.6062500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>36.84375</v>
+        <v>36.22</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.50625</v>
+        <v>0.50125</v>
       </c>
       <c r="N7" t="n">
-        <v>36.61875</v>
+        <v>36.35125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.41125</v>
+        <v>0.45875</v>
       </c>
       <c r="N8" t="n">
-        <v>36.775</v>
+        <v>36.78375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8048</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>374</v>
+      </c>
+      <c r="D75" t="n">
+        <v>248</v>
+      </c>
+      <c r="E75" t="n">
+        <v>126</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>67</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>70</v>
+      </c>
+      <c r="K75" t="n">
+        <v>56</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6399999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.002077767883644999</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1047120418848166</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
